--- a/artfynd/A 63038-2025 artfynd.xlsx
+++ b/artfynd/A 63038-2025 artfynd.xlsx
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133398509</v>
+        <v>133398672</v>
       </c>
       <c r="B6" t="n">
-        <v>79365</v>
+        <v>80438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592711</v>
+        <v>592785</v>
       </c>
       <c r="R6" t="n">
-        <v>6999291</v>
+        <v>6999311</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133398672</v>
+        <v>133398509</v>
       </c>
       <c r="B7" t="n">
-        <v>80438</v>
+        <v>79365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592785</v>
+        <v>592711</v>
       </c>
       <c r="R7" t="n">
-        <v>6999311</v>
+        <v>6999291</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 63038-2025 artfynd.xlsx
+++ b/artfynd/A 63038-2025 artfynd.xlsx
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133398672</v>
+        <v>133398509</v>
       </c>
       <c r="B6" t="n">
-        <v>80438</v>
+        <v>79365</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592785</v>
+        <v>592711</v>
       </c>
       <c r="R6" t="n">
-        <v>6999311</v>
+        <v>6999291</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133398509</v>
+        <v>133398672</v>
       </c>
       <c r="B7" t="n">
-        <v>79365</v>
+        <v>80438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592711</v>
+        <v>592785</v>
       </c>
       <c r="R7" t="n">
-        <v>6999291</v>
+        <v>6999311</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133398686</v>
+        <v>133398755</v>
       </c>
       <c r="B8" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592786</v>
+        <v>592739</v>
       </c>
       <c r="R8" t="n">
-        <v>6999272</v>
+        <v>6999268</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133398755</v>
+        <v>133398686</v>
       </c>
       <c r="B9" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592739</v>
+        <v>592786</v>
       </c>
       <c r="R9" t="n">
-        <v>6999268</v>
+        <v>6999272</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 63038-2025 artfynd.xlsx
+++ b/artfynd/A 63038-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133398785</v>
+        <v>133398509</v>
       </c>
       <c r="B2" t="n">
-        <v>99095</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592736</v>
+        <v>592711</v>
       </c>
       <c r="R2" t="n">
-        <v>6999307</v>
+        <v>6999291</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133398560</v>
+        <v>133398772</v>
       </c>
       <c r="B3" t="n">
-        <v>80478</v>
+        <v>83222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592795</v>
+        <v>592708</v>
       </c>
       <c r="R3" t="n">
-        <v>6999336</v>
+        <v>6999301</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133398779</v>
+        <v>133398755</v>
       </c>
       <c r="B4" t="n">
-        <v>83207</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592708</v>
+        <v>592739</v>
       </c>
       <c r="R4" t="n">
-        <v>6999301</v>
+        <v>6999268</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133398671</v>
+        <v>133398669</v>
       </c>
       <c r="B5" t="n">
-        <v>80473</v>
+        <v>80488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592802</v>
+        <v>592786</v>
       </c>
       <c r="R5" t="n">
-        <v>6999335</v>
+        <v>6999272</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133398509</v>
+        <v>133398670</v>
       </c>
       <c r="B6" t="n">
-        <v>79390</v>
+        <v>80488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592711</v>
+        <v>592889</v>
       </c>
       <c r="R6" t="n">
-        <v>6999291</v>
+        <v>6999274</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133398672</v>
+        <v>133398671</v>
       </c>
       <c r="B7" t="n">
-        <v>80473</v>
+        <v>80488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592785</v>
+        <v>592802</v>
       </c>
       <c r="R7" t="n">
-        <v>6999311</v>
+        <v>6999335</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133398686</v>
+        <v>133398672</v>
       </c>
       <c r="B8" t="n">
-        <v>80473</v>
+        <v>80488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592786</v>
+        <v>592785</v>
       </c>
       <c r="R8" t="n">
-        <v>6999272</v>
+        <v>6999311</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133398755</v>
+        <v>133398673</v>
       </c>
       <c r="B9" t="n">
-        <v>79358</v>
+        <v>80488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592739</v>
+        <v>592690</v>
       </c>
       <c r="R9" t="n">
-        <v>6999268</v>
+        <v>6999308</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133398673</v>
+        <v>133398553</v>
       </c>
       <c r="B10" t="n">
-        <v>80473</v>
+        <v>80493</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592690</v>
+        <v>592795</v>
       </c>
       <c r="R10" t="n">
-        <v>6999308</v>
+        <v>6999336</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1545,6 +1545,103 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133398781</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>592736</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6999307</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tim Nordvall</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tim Nordvall</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63038-2025 artfynd.xlsx
+++ b/artfynd/A 63038-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133398509</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133398772</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133398755</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133398669</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133398670</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133398671</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133398672</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133398673</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133398553</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,8 +1692,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133398781</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>